--- a/data/trans_camb/P1417-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1417-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,28</t>
+          <t>-1,06; 0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,35</t>
+          <t>-0,35; 1,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,86</t>
+          <t>0,36; 2,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,56</t>
+          <t>-0,57; 2,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,25</t>
+          <t>-0,13; 3,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,59</t>
+          <t>0,79; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,18</t>
+          <t>-0,44; 1,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,82</t>
+          <t>0,06; 1,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,43</t>
+          <t>0,89; 2,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272,45%</t>
+          <t>332,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>136,12%</t>
+          <t>143,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>166,35%</t>
+          <t>183,42%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,46; —</t>
+          <t>-23,32; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 274,85</t>
+          <t>-30,78; 238,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 351,8</t>
+          <t>-15,03; 315,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,96; 421,68</t>
+          <t>23,25; 365,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 170,06</t>
+          <t>-35,82; 191,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 279,46</t>
+          <t>-1,59; 311,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,32; 368,05</t>
+          <t>56,61; 436,03</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,14</t>
+          <t>-0,15; 1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,2</t>
+          <t>-0,14; 1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,65</t>
+          <t>0,49; 1,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,32</t>
+          <t>0,61; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,95</t>
+          <t>-0,4; 1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,26</t>
+          <t>1,59; 3,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,87</t>
+          <t>0,42; 2,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,29</t>
+          <t>-0,07; 1,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,6</t>
+          <t>1,28; 2,8</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>287,87%</t>
+          <t>367,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>222,91%</t>
+          <t>216,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>214,78%</t>
+          <t>247,01%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,53; —</t>
+          <t>-58,77; 1023,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 1262,76</t>
+          <t>-43,51; 1041,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 1411,85</t>
+          <t>43,85; 1636,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,89; 379,14</t>
+          <t>30,92; 449,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 237,33</t>
+          <t>-26,5; 253,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,14; 540,81</t>
+          <t>73,69; 490,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,89; 340,66</t>
+          <t>30,28; 377,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 240,35</t>
+          <t>-9,51; 248,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,57; 490,54</t>
+          <t>105,83; 537,21</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,27</t>
+          <t>-1,25; 0,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,98</t>
+          <t>-0,67; 1,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,61</t>
+          <t>-0,24; 1,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,66</t>
+          <t>-1,85; 1,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,95</t>
+          <t>-2,39; 1,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,33</t>
+          <t>1,17; 5,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,79</t>
+          <t>-1,14; 0,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,7</t>
+          <t>-1,14; 0,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,88</t>
+          <t>0,76; 3,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167,57%</t>
+          <t>168,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>110,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>117,93%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,5; —</t>
+          <t>-76,79; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 99,36</t>
+          <t>-51,09; 96,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 52,91</t>
+          <t>-62,05; 61,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 210,2</t>
+          <t>25,97; 317,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 76,72</t>
+          <t>-51,92; 71,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 67,23</t>
+          <t>-52,58; 71,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 250,88</t>
+          <t>29,75; 273,22</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,78</t>
+          <t>-0,51; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; -0,07</t>
+          <t>-1,01; -0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,03</t>
+          <t>-0,33; 0,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,12</t>
+          <t>-0,15; 2,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,59</t>
+          <t>-0,04; 2,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,03</t>
+          <t>1,6; 4,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,24</t>
+          <t>-0,15; 1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,21</t>
+          <t>-0,29; 1,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,39</t>
+          <t>0,96; 2,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185,1%</t>
+          <t>198,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>157,47%</t>
+          <t>165,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,77; 353,73</t>
+          <t>-66,01; 432,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 439,6</t>
+          <t>-46,78; 410,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 216,09</t>
+          <t>-10,04; 223,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 261,33</t>
+          <t>-8,65; 262,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,44; 442,67</t>
+          <t>67,11; 451,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 170,43</t>
+          <t>-14,38; 164,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 173,93</t>
+          <t>-20,76; 148,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,25; 336,29</t>
+          <t>67,39; 343,25</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,49</t>
+          <t>-0,21; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,1</t>
+          <t>0,45; 1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,72</t>
+          <t>0,29; 1,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,5</t>
+          <t>0,06; 1,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,37</t>
+          <t>2,06; 3,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,91</t>
+          <t>0,16; 0,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,07</t>
+          <t>1,44; 2,3</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172,7%</t>
+          <t>201,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>145,44%</t>
+          <t>164,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>152,42%</t>
+          <t>173,61%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 128,77</t>
+          <t>-52,01; 141,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 186,55</t>
+          <t>-41,02; 184,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,29; 445,22</t>
+          <t>62,96; 473,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,85; 122,3</t>
+          <t>12,48; 121,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,4; 111,45</t>
+          <t>1,59; 103,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,31; 246,6</t>
+          <t>100,35; 265,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,66; 102,72</t>
+          <t>11,62; 104,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,58; 97,22</t>
+          <t>6,17; 97,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>88,57; 234,71</t>
+          <t>108,79; 262,21</t>
         </is>
       </c>
     </row>
